--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>昵称</t>
   </si>
@@ -80,10 +80,7 @@
     <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
   </si>
   <si>
-    <t>ubs</t>
-  </si>
-  <si>
-    <t>0x9ee11a802B593B053a8489Fb27F6fc3b9c0262B8</t>
+    <t>kevin隱月(UBS)</t>
   </si>
   <si>
     <t>鞋神</t>
@@ -113,7 +110,7 @@
     <t>0x99561e3080385C907c4A9B4bbB944508E8d1D15e</t>
   </si>
   <si>
-    <t>kevin隱月</t>
+    <t>kevin隱月(去B組)</t>
   </si>
   <si>
     <t>傑哥</t>
@@ -132,6 +129,42 @@
   </si>
   <si>
     <t>0xA533F7729940DD9402da699aa8a9bD3281181FfC</t>
+  </si>
+  <si>
+    <t>muuame</t>
+  </si>
+  <si>
+    <t>0x76daf610E09B31407244841e2A97682a32f32463</t>
+  </si>
+  <si>
+    <t>Osora</t>
+  </si>
+  <si>
+    <t>0x01e11d2925519f6C84EA49B6809f3D34b87a43Df</t>
+  </si>
+  <si>
+    <t>MrKun</t>
+  </si>
+  <si>
+    <t>0xcb5C82d2fd95C35d4CAe44a2a5CD44C9b1201A87</t>
+  </si>
+  <si>
+    <t>Number17</t>
+  </si>
+  <si>
+    <t>0xbD015CC6F657D0D2c54dE363A9117a7f2db147A1</t>
+  </si>
+  <si>
+    <t>magisa</t>
+  </si>
+  <si>
+    <t>0x6f6E91a883A9Ec32068302a4051B27C57E376A48</t>
+  </si>
+  <si>
+    <t>Uuaa</t>
+  </si>
+  <si>
+    <t>0x28C6D23Ed651576c6b3e0DFd6B88dDbe5c7eC4Dc</t>
   </si>
 </sst>
 </file>
@@ -144,7 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -159,8 +192,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF171717"/>
+      <name val="Inter"/>
       <charset val="134"/>
     </font>
     <font>
@@ -315,7 +353,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +363,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF182232"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6B8AF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,160 +700,172 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1071,7 +1145,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AddressBook" displayName="AddressBook" ref="A1:B19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AddressBook" displayName="AddressBook" ref="A1:B25">
   <tableColumns count="2">
     <tableColumn id="1" name="昵称"/>
     <tableColumn id="2" name="地址"/>
@@ -1229,7 +1303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="23.55" customWidth="1"/>
@@ -1293,99 +1367,147 @@
       </c>
     </row>
     <row r="8" ht="15" spans="1:2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:2">
+      <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" ht="15" spans="1:2">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="12" ht="15" spans="1:2">
+      <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" ht="15" spans="1:2">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="13" ht="15" spans="1:2">
+      <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" ht="15" spans="1:2">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="14" ht="15" spans="1:2">
+      <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" ht="15" spans="1:2">
-      <c r="A14" s="3" t="s">
+      <c r="B14" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:2">
+      <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:2">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="3" t="s">
+    </row>
+    <row r="16" ht="15" spans="1:2">
+      <c r="A16" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" ht="15" spans="1:2">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:2">
+      <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:2">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="3" t="s">
+    </row>
+    <row r="18" ht="15" spans="1:2">
+      <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" ht="15" spans="1:2">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="3" t="s">
+    </row>
+    <row r="19" ht="15" spans="1:2">
+      <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" ht="15" spans="1:2">
-      <c r="A19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="20" ht="15" spans="1:2">
+      <c r="A20" s="6" t="s">
         <v>34</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:2">
+      <c r="A21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:2">
+      <c r="A22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:2">
+      <c r="A23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:2">
+      <c r="A24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:2">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43CA2712-3B86-4253-8C08-E2017C2D4591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003D299A-01BA-4D0B-A225-903052512865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>ManhACE</t>
   </si>
@@ -102,6 +102,147 @@
   </si>
   <si>
     <t>0x8Dcaeb54Ebc684F924B2ae285281c98569E02326</t>
+  </si>
+  <si>
+    <t>EatShoes</t>
+  </si>
+  <si>
+    <t>0x43E019261b6C627fDdF91c8012AcC9F0C56e99c7</t>
+  </si>
+  <si>
+    <t>kakakakakak1</t>
+  </si>
+  <si>
+    <t>IUnar</t>
+  </si>
+  <si>
+    <t>0xE9E5e18DcB7932188f863d421c7aB8491a021175</t>
+  </si>
+  <si>
+    <t>Pokerman</t>
+  </si>
+  <si>
+    <t>0x7109670b65c1aeECb251D67407Af8cDF1e001185</t>
+  </si>
+  <si>
+    <t>DevilCase</t>
+  </si>
+  <si>
+    <t>o8888888</t>
+  </si>
+  <si>
+    <t>0x940Fbb99e06A4eDBd403ec2BdaC652F6e5eadda3</t>
+  </si>
+  <si>
+    <t>muuame</t>
+  </si>
+  <si>
+    <t>0x76daf610E09B31407244841e2A97682a32f32463</t>
+  </si>
+  <si>
+    <t>Lightbringer</t>
+  </si>
+  <si>
+    <t>0x99561e3080385C907c4A9B4bbB944508E8d1D15e</t>
+  </si>
+  <si>
+    <t>Osora</t>
+  </si>
+  <si>
+    <t>0x01e11d2925519f6C84EA49B6809f3D34b87a43Df</t>
+  </si>
+  <si>
+    <t>asdwqa12</t>
+  </si>
+  <si>
+    <t>0xA533F7729940DD9402da699aa8a9bD3281181FfC</t>
+  </si>
+  <si>
+    <t>Number17</t>
+  </si>
+  <si>
+    <t>0xbD015CC6F657D0D2c54dE363A9117a7f2db147A1</t>
+  </si>
+  <si>
+    <t>magisa</t>
+  </si>
+  <si>
+    <t>0x6f6E91a883A9Ec32068302a4051B27C57E376A48</t>
+  </si>
+  <si>
+    <t>MrKun</t>
+  </si>
+  <si>
+    <t>0xcb5C82d2fd95C35d4CAe44a2a5CD44C9b1201A87</t>
+  </si>
+  <si>
+    <t>INurseI</t>
+  </si>
+  <si>
+    <t>0xbF543fB6fe42f1c54A01385298c29D3Fba735951</t>
+  </si>
+  <si>
+    <t>Mitsuya</t>
+  </si>
+  <si>
+    <t>0xA5a0FeABD47B1865ba0a402abcfC810a7A560d06</t>
+  </si>
+  <si>
+    <t>ShadowSAMA</t>
+  </si>
+  <si>
+    <t>0x1db18A653bd7C6C2dc899933340B7a960b451399</t>
+  </si>
+  <si>
+    <t>ouwen110</t>
+  </si>
+  <si>
+    <t>0x37CA68Bcd9fd3f13CB732a3307ed64233F96a02d</t>
+  </si>
+  <si>
+    <t>NFT188</t>
+  </si>
+  <si>
+    <t>0x34219BDBfDcB233FCe08185724435fDd40E89929</t>
+  </si>
+  <si>
+    <t>KCOF</t>
+  </si>
+  <si>
+    <t>0x8E804BD15403d74C294752D66d970744876C5146</t>
+  </si>
+  <si>
+    <t>SoLUK</t>
+  </si>
+  <si>
+    <t>0x9bCeE51c0AEd896CAAb5fb6B7FB6630D1101Edd8</t>
+  </si>
+  <si>
+    <t>xQvQx</t>
+  </si>
+  <si>
+    <t>0xdf01a3312df58fA7B689Ce3fa1eFd9c0422171Bf</t>
+  </si>
+  <si>
+    <t>dXwXb</t>
+  </si>
+  <si>
+    <t>0xD8cc71d298F3A6f3D497357963Ac4723fc81FB8e</t>
+  </si>
+  <si>
+    <t>kappy</t>
+  </si>
+  <si>
+    <t>0xD63E33fB919d4dC190aD5c980DF71d3aF334DcA1</t>
+  </si>
+  <si>
+    <t>JBJOuO</t>
+  </si>
+  <si>
+    <t>0xB1cc3f69F8A6C965893B0398ab857475F367d2f1</t>
+  </si>
+  <si>
+    <t>chan9q</t>
   </si>
 </sst>
 </file>
@@ -485,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21573F96-787D-43CE-A4C4-3589456289B8}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -576,6 +717,206 @@
         <v>20</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003D299A-01BA-4D0B-A225-903052512865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDC33A3D-0577-422C-A376-D291FF4A91F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84EB4D0B-46EA-4EB7-A886-40161CF1B955}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,73 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+  <si>
+    <t>Findlay</t>
+  </si>
+  <si>
+    <t>0x0067365bDaA8DBFaa683C385623896fe5C5E83f3</t>
+  </si>
+  <si>
+    <t>o8888888</t>
+  </si>
+  <si>
+    <t>0x940Fbb99e06A4eDBd403ec2BdaC652F6e5eadda3</t>
+  </si>
+  <si>
+    <t>Pokerman</t>
+  </si>
+  <si>
+    <t>0x7109670b65c1aeECb251D67407Af8cDF1e001185</t>
+  </si>
+  <si>
+    <t>Mitsuya</t>
+  </si>
+  <si>
+    <t>0xA5a0FeABD47B1865ba0a402abcfC810a7A560d06</t>
+  </si>
+  <si>
+    <t>MeiFu</t>
+  </si>
+  <si>
+    <t>0x93DcB573b9578D531B31cA1d6E33c935bA668423</t>
+  </si>
+  <si>
+    <t>kenyek</t>
+  </si>
+  <si>
+    <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
+  </si>
+  <si>
+    <t>LiuDeHua</t>
+  </si>
+  <si>
+    <t>0x0a1364c754dfBcC04dfDCd84C4c771cA697FeD76</t>
+  </si>
+  <si>
+    <t>Powder</t>
+  </si>
+  <si>
+    <t>0x7292FC4dCeA35666d638A23F519406A5E634Fd05</t>
+  </si>
+  <si>
+    <t>DevilCase</t>
+  </si>
+  <si>
+    <t>0x1a83fF0698FaaCef459BfB6945b7D23a0B0919Cd</t>
+  </si>
+  <si>
+    <t>LunLunSaint</t>
+  </si>
+  <si>
+    <t>0x61b72F9dC73CaAD654fF9F24d9eEB11A2b730f45</t>
+  </si>
+  <si>
+    <t>NFT188</t>
+  </si>
+  <si>
+    <t>0x34219BDBfDcB233FCe08185724435fDd40E89929</t>
+  </si>
   <si>
     <t>ManhACE</t>
   </si>
@@ -47,97 +113,94 @@
     <t>0x0d07c525829614509506c843813225342FE9023e</t>
   </si>
   <si>
+    <t>INurseI</t>
+  </si>
+  <si>
+    <t>0xbF543fB6fe42f1c54A01385298c29D3Fba735951</t>
+  </si>
+  <si>
+    <t>Polestarr</t>
+  </si>
+  <si>
+    <t>0x8Dcaeb54Ebc684F924B2ae285281c98569E02326</t>
+  </si>
+  <si>
+    <t>xQvQx</t>
+  </si>
+  <si>
+    <t>0xdf01a3312df58fA7B689Ce3fa1eFd9c0422171Bf</t>
+  </si>
+  <si>
+    <t>ptzO3O7</t>
+  </si>
+  <si>
+    <t>0x824EDB61C934E23b3fe03865eD72fa35BFAe7693</t>
+  </si>
+  <si>
+    <t>ShadowSAMA</t>
+  </si>
+  <si>
+    <t>0x1db18A653bd7C6C2dc899933340B7a960b451399</t>
+  </si>
+  <si>
+    <t>EatShoes</t>
+  </si>
+  <si>
+    <t>0x43E019261b6C627fDdF91c8012AcC9F0C56e99c7</t>
+  </si>
+  <si>
+    <t>MrKun</t>
+  </si>
+  <si>
+    <t>0xcb5C82d2fd95C35d4CAe44a2a5CD44C9b1201A87</t>
+  </si>
+  <si>
     <t>BIG1996</t>
   </si>
   <si>
     <t>0x2722f1d45e7337bA945dfF885623eFf744fdE805</t>
   </si>
   <si>
-    <t>LunLunSaint</t>
-  </si>
-  <si>
-    <t>0x61b72F9dC73CaAD654fF9F24d9eEB11A2b730f45</t>
+    <t>chan9q</t>
+  </si>
+  <si>
+    <t>SoLUK</t>
+  </si>
+  <si>
+    <t>0x9bCeE51c0AEd896CAAb5fb6B7FB6630D1101Edd8</t>
+  </si>
+  <si>
+    <t>OkamiPulsard</t>
+  </si>
+  <si>
+    <t>0x036f36547917798d440BB50232839EbC2b36A054</t>
+  </si>
+  <si>
+    <t>EVMs</t>
+  </si>
+  <si>
+    <t>0x4F64F34b61bf78b8aEDd31026B974BCB2bf73A35</t>
   </si>
   <si>
     <t>KitaKitsune</t>
   </si>
   <si>
-    <t>0x1a83fF0698FaaCef459BfB6945b7D23a0B0919Cd</t>
-  </si>
-  <si>
-    <t>TheLasT</t>
-  </si>
-  <si>
-    <t>0xD3609eE3fBCF7923b3B101E8AfB7b215459d7eF8</t>
-  </si>
-  <si>
-    <t>WhiteNights</t>
-  </si>
-  <si>
-    <t>Powder</t>
-  </si>
-  <si>
-    <t>0x7292FC4dCeA35666d638A23F519406A5E634Fd05</t>
-  </si>
-  <si>
-    <t>MeiFu</t>
-  </si>
-  <si>
-    <t>0x93DcB573b9578D531B31cA1d6E33c935bA668423</t>
-  </si>
-  <si>
-    <t>LiuDeHua</t>
-  </si>
-  <si>
-    <t>0x0a1364c754dfBcC04dfDCd84C4c771cA697FeD76</t>
-  </si>
-  <si>
-    <t>kenyek</t>
-  </si>
-  <si>
-    <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
-  </si>
-  <si>
-    <t>Polestarr</t>
-  </si>
-  <si>
-    <t>0x8Dcaeb54Ebc684F924B2ae285281c98569E02326</t>
-  </si>
-  <si>
-    <t>EatShoes</t>
-  </si>
-  <si>
-    <t>0x43E019261b6C627fDdF91c8012AcC9F0C56e99c7</t>
-  </si>
-  <si>
-    <t>kakakakakak1</t>
-  </si>
-  <si>
-    <t>IUnar</t>
-  </si>
-  <si>
-    <t>0xE9E5e18DcB7932188f863d421c7aB8491a021175</t>
-  </si>
-  <si>
-    <t>Pokerman</t>
-  </si>
-  <si>
-    <t>0x7109670b65c1aeECb251D67407Af8cDF1e001185</t>
-  </si>
-  <si>
-    <t>DevilCase</t>
-  </si>
-  <si>
-    <t>o8888888</t>
-  </si>
-  <si>
-    <t>0x940Fbb99e06A4eDBd403ec2BdaC652F6e5eadda3</t>
-  </si>
-  <si>
-    <t>muuame</t>
-  </si>
-  <si>
-    <t>0x76daf610E09B31407244841e2A97682a32f32463</t>
+    <t>Osora</t>
+  </si>
+  <si>
+    <t>0x01e11d2925519f6C84EA49B6809f3D34b87a43Df</t>
+  </si>
+  <si>
+    <t>Number17</t>
+  </si>
+  <si>
+    <t>0xbD015CC6F657D0D2c54dE363A9117a7f2db147A1</t>
+  </si>
+  <si>
+    <t>magisa</t>
+  </si>
+  <si>
+    <t>0x6f6E91a883A9Ec32068302a4051B27C57E376A48</t>
   </si>
   <si>
     <t>Lightbringer</t>
@@ -146,110 +209,44 @@
     <t>0x99561e3080385C907c4A9B4bbB944508E8d1D15e</t>
   </si>
   <si>
-    <t>Osora</t>
-  </si>
-  <si>
-    <t>0x01e11d2925519f6C84EA49B6809f3D34b87a43Df</t>
+    <t>LuckyFox66</t>
+  </si>
+  <si>
+    <t>ningyiyi</t>
+  </si>
+  <si>
+    <t>0x10AEF2E22EbCbCBA5f4C00122F14aEEE3E0452a7</t>
+  </si>
+  <si>
+    <t>Sumire</t>
+  </si>
+  <si>
+    <t>0x7f982521Aa5e3e0f16d6FF882623f98a316d0E70</t>
+  </si>
+  <si>
+    <t>iiTzWasabi</t>
+  </si>
+  <si>
+    <t>0xf33fc5245372149f26159C28cA674FE0169A1018</t>
+  </si>
+  <si>
+    <t>EliteArrow</t>
+  </si>
+  <si>
+    <t>0x88355C236580e126Bbd75956100347c8664285D1</t>
   </si>
   <si>
     <t>asdwqa12</t>
   </si>
   <si>
     <t>0xA533F7729940DD9402da699aa8a9bD3281181FfC</t>
-  </si>
-  <si>
-    <t>Number17</t>
-  </si>
-  <si>
-    <t>0xbD015CC6F657D0D2c54dE363A9117a7f2db147A1</t>
-  </si>
-  <si>
-    <t>magisa</t>
-  </si>
-  <si>
-    <t>0x6f6E91a883A9Ec32068302a4051B27C57E376A48</t>
-  </si>
-  <si>
-    <t>MrKun</t>
-  </si>
-  <si>
-    <t>0xcb5C82d2fd95C35d4CAe44a2a5CD44C9b1201A87</t>
-  </si>
-  <si>
-    <t>INurseI</t>
-  </si>
-  <si>
-    <t>0xbF543fB6fe42f1c54A01385298c29D3Fba735951</t>
-  </si>
-  <si>
-    <t>Mitsuya</t>
-  </si>
-  <si>
-    <t>0xA5a0FeABD47B1865ba0a402abcfC810a7A560d06</t>
-  </si>
-  <si>
-    <t>ShadowSAMA</t>
-  </si>
-  <si>
-    <t>0x1db18A653bd7C6C2dc899933340B7a960b451399</t>
-  </si>
-  <si>
-    <t>ouwen110</t>
-  </si>
-  <si>
-    <t>0x37CA68Bcd9fd3f13CB732a3307ed64233F96a02d</t>
-  </si>
-  <si>
-    <t>NFT188</t>
-  </si>
-  <si>
-    <t>0x34219BDBfDcB233FCe08185724435fDd40E89929</t>
-  </si>
-  <si>
-    <t>KCOF</t>
-  </si>
-  <si>
-    <t>0x8E804BD15403d74C294752D66d970744876C5146</t>
-  </si>
-  <si>
-    <t>SoLUK</t>
-  </si>
-  <si>
-    <t>0x9bCeE51c0AEd896CAAb5fb6B7FB6630D1101Edd8</t>
-  </si>
-  <si>
-    <t>xQvQx</t>
-  </si>
-  <si>
-    <t>0xdf01a3312df58fA7B689Ce3fa1eFd9c0422171Bf</t>
-  </si>
-  <si>
-    <t>dXwXb</t>
-  </si>
-  <si>
-    <t>0xD8cc71d298F3A6f3D497357963Ac4723fc81FB8e</t>
-  </si>
-  <si>
-    <t>kappy</t>
-  </si>
-  <si>
-    <t>0xD63E33fB919d4dC190aD5c980DF71d3aF334DcA1</t>
-  </si>
-  <si>
-    <t>JBJOuO</t>
-  </si>
-  <si>
-    <t>0xB1cc3f69F8A6C965893B0398ab857475F367d2f1</t>
-  </si>
-  <si>
-    <t>chan9q</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -265,6 +262,18 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -274,12 +283,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -288,9 +312,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,296 +655,288 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21573F96-787D-43CE-A4C4-3589456289B8}">
-  <dimension ref="A1:B36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F34DBE1-EA72-4533-97B0-9D4EFF35C954}">
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="14" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="15" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="23" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B23" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="24" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B24" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="25" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="28" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="29" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDC33A3D-0577-422C-A376-D291FF4A91F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9824A7-8A35-47C7-8872-1C8CFB59A5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84EB4D0B-46EA-4EB7-A886-40161CF1B955}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,145 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+  <si>
+    <t>ManhACE</t>
+  </si>
+  <si>
+    <t>0x0d07c525829614509506c843813225342FE9023e</t>
+  </si>
+  <si>
+    <t>BIG1996</t>
+  </si>
+  <si>
+    <t>0x2722f1d45e7337bA945dfF885623eFf744fdE805</t>
+  </si>
+  <si>
+    <t>LunLunSaint</t>
+  </si>
+  <si>
+    <t>0x61b72F9dC73CaAD654fF9F24d9eEB11A2b730f45</t>
+  </si>
+  <si>
+    <t>Powder</t>
+  </si>
+  <si>
+    <t>0x7292FC4dCeA35666d638A23F519406A5E634Fd05</t>
+  </si>
+  <si>
+    <t>MeiFu</t>
+  </si>
+  <si>
+    <t>0x93DcB573b9578D531B31cA1d6E33c935bA668423</t>
+  </si>
+  <si>
+    <t>LiuDeHua</t>
+  </si>
+  <si>
+    <t>0x0a1364c754dfBcC04dfDCd84C4c771cA697FeD76</t>
+  </si>
+  <si>
+    <t>kenyek</t>
+  </si>
+  <si>
+    <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
+  </si>
+  <si>
+    <t>Polestarr</t>
+  </si>
+  <si>
+    <t>0x8Dcaeb54Ebc684F924B2ae285281c98569E02326</t>
+  </si>
+  <si>
+    <t>EatShoes</t>
+  </si>
+  <si>
+    <t>0x43E019261b6C627fDdF91c8012AcC9F0C56e99c7</t>
+  </si>
+  <si>
+    <t>Pokerman</t>
+  </si>
+  <si>
+    <t>0x7109670b65c1aeECb251D67407Af8cDF1e001185</t>
+  </si>
+  <si>
+    <t>DevilCase</t>
+  </si>
+  <si>
+    <t>o8888888</t>
+  </si>
+  <si>
+    <t>0x940Fbb99e06A4eDBd403ec2BdaC652F6e5eadda3</t>
+  </si>
+  <si>
+    <t>Lightbringer</t>
+  </si>
+  <si>
+    <t>0x99561e3080385C907c4A9B4bbB944508E8d1D15e</t>
+  </si>
+  <si>
+    <t>Osora</t>
+  </si>
+  <si>
+    <t>0x01e11d2925519f6C84EA49B6809f3D34b87a43Df</t>
+  </si>
+  <si>
+    <t>asdwqa12</t>
+  </si>
+  <si>
+    <t>0xA533F7729940DD9402da699aa8a9bD3281181FfC</t>
+  </si>
+  <si>
+    <t>Number17</t>
+  </si>
+  <si>
+    <t>0xbD015CC6F657D0D2c54dE363A9117a7f2db147A1</t>
+  </si>
+  <si>
+    <t>magisa</t>
+  </si>
+  <si>
+    <t>0x6f6E91a883A9Ec32068302a4051B27C57E376A48</t>
+  </si>
+  <si>
+    <t>MrKun</t>
+  </si>
+  <si>
+    <t>0xcb5C82d2fd95C35d4CAe44a2a5CD44C9b1201A87</t>
+  </si>
+  <si>
+    <t>INurseI</t>
+  </si>
+  <si>
+    <t>0xbF543fB6fe42f1c54A01385298c29D3Fba735951</t>
+  </si>
+  <si>
+    <t>ShadowSAMA</t>
+  </si>
+  <si>
+    <t>0x1db18A653bd7C6C2dc899933340B7a960b451399</t>
+  </si>
+  <si>
+    <t>NFT188</t>
+  </si>
+  <si>
+    <t>0x34219BDBfDcB233FCe08185724435fDd40E89929</t>
+  </si>
+  <si>
+    <t>SoLUK</t>
+  </si>
+  <si>
+    <t>0x9bCeE51c0AEd896CAAb5fb6B7FB6630D1101Edd8</t>
+  </si>
+  <si>
+    <t>xQvQx</t>
+  </si>
+  <si>
+    <t>0xdf01a3312df58fA7B689Ce3fa1eFd9c0422171Bf</t>
+  </si>
+  <si>
+    <t>chan9q</t>
+  </si>
   <si>
     <t>Findlay</t>
   </si>
@@ -47,88 +185,7 @@
     <t>0x0067365bDaA8DBFaa683C385623896fe5C5E83f3</t>
   </si>
   <si>
-    <t>o8888888</t>
-  </si>
-  <si>
-    <t>0x940Fbb99e06A4eDBd403ec2BdaC652F6e5eadda3</t>
-  </si>
-  <si>
-    <t>Pokerman</t>
-  </si>
-  <si>
-    <t>0x7109670b65c1aeECb251D67407Af8cDF1e001185</t>
-  </si>
-  <si>
-    <t>Mitsuya</t>
-  </si>
-  <si>
-    <t>0xA5a0FeABD47B1865ba0a402abcfC810a7A560d06</t>
-  </si>
-  <si>
-    <t>MeiFu</t>
-  </si>
-  <si>
-    <t>0x93DcB573b9578D531B31cA1d6E33c935bA668423</t>
-  </si>
-  <si>
-    <t>kenyek</t>
-  </si>
-  <si>
-    <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
-  </si>
-  <si>
-    <t>LiuDeHua</t>
-  </si>
-  <si>
-    <t>0x0a1364c754dfBcC04dfDCd84C4c771cA697FeD76</t>
-  </si>
-  <si>
-    <t>Powder</t>
-  </si>
-  <si>
-    <t>0x7292FC4dCeA35666d638A23F519406A5E634Fd05</t>
-  </si>
-  <si>
-    <t>DevilCase</t>
-  </si>
-  <si>
-    <t>0x1a83fF0698FaaCef459BfB6945b7D23a0B0919Cd</t>
-  </si>
-  <si>
-    <t>LunLunSaint</t>
-  </si>
-  <si>
-    <t>0x61b72F9dC73CaAD654fF9F24d9eEB11A2b730f45</t>
-  </si>
-  <si>
-    <t>NFT188</t>
-  </si>
-  <si>
-    <t>0x34219BDBfDcB233FCe08185724435fDd40E89929</t>
-  </si>
-  <si>
-    <t>ManhACE</t>
-  </si>
-  <si>
-    <t>0x0d07c525829614509506c843813225342FE9023e</t>
-  </si>
-  <si>
-    <t>INurseI</t>
-  </si>
-  <si>
-    <t>0xbF543fB6fe42f1c54A01385298c29D3Fba735951</t>
-  </si>
-  <si>
-    <t>Polestarr</t>
-  </si>
-  <si>
-    <t>0x8Dcaeb54Ebc684F924B2ae285281c98569E02326</t>
-  </si>
-  <si>
-    <t>xQvQx</t>
-  </si>
-  <si>
-    <t>0xdf01a3312df58fA7B689Ce3fa1eFd9c0422171Bf</t>
+    <t>0x76807A4d1b91eC1bF43B58d0776Bd8A1693b662c</t>
   </si>
   <si>
     <t>ptzO3O7</t>
@@ -137,39 +194,6 @@
     <t>0x824EDB61C934E23b3fe03865eD72fa35BFAe7693</t>
   </si>
   <si>
-    <t>ShadowSAMA</t>
-  </si>
-  <si>
-    <t>0x1db18A653bd7C6C2dc899933340B7a960b451399</t>
-  </si>
-  <si>
-    <t>EatShoes</t>
-  </si>
-  <si>
-    <t>0x43E019261b6C627fDdF91c8012AcC9F0C56e99c7</t>
-  </si>
-  <si>
-    <t>MrKun</t>
-  </si>
-  <si>
-    <t>0xcb5C82d2fd95C35d4CAe44a2a5CD44C9b1201A87</t>
-  </si>
-  <si>
-    <t>BIG1996</t>
-  </si>
-  <si>
-    <t>0x2722f1d45e7337bA945dfF885623eFf744fdE805</t>
-  </si>
-  <si>
-    <t>chan9q</t>
-  </si>
-  <si>
-    <t>SoLUK</t>
-  </si>
-  <si>
-    <t>0x9bCeE51c0AEd896CAAb5fb6B7FB6630D1101Edd8</t>
-  </si>
-  <si>
     <t>OkamiPulsard</t>
   </si>
   <si>
@@ -182,31 +206,16 @@
     <t>0x4F64F34b61bf78b8aEDd31026B974BCB2bf73A35</t>
   </si>
   <si>
-    <t>KitaKitsune</t>
-  </si>
-  <si>
-    <t>Osora</t>
-  </si>
-  <si>
-    <t>0x01e11d2925519f6C84EA49B6809f3D34b87a43Df</t>
-  </si>
-  <si>
-    <t>Number17</t>
-  </si>
-  <si>
-    <t>0xbD015CC6F657D0D2c54dE363A9117a7f2db147A1</t>
-  </si>
-  <si>
-    <t>magisa</t>
-  </si>
-  <si>
-    <t>0x6f6E91a883A9Ec32068302a4051B27C57E376A48</t>
-  </si>
-  <si>
-    <t>Lightbringer</t>
-  </si>
-  <si>
-    <t>0x99561e3080385C907c4A9B4bbB944508E8d1D15e</t>
+    <t>Sazabi</t>
+  </si>
+  <si>
+    <t>0x04B0fc4784577C117CF1b4A18Bb7316072Aff59C</t>
+  </si>
+  <si>
+    <t>Plume</t>
+  </si>
+  <si>
+    <t>0x479bF9bD2dEe2CFD235049F4718E5d9d31D5dB74</t>
   </si>
   <si>
     <t>LuckyFox66</t>
@@ -234,19 +243,13 @@
   </si>
   <si>
     <t>0x88355C236580e126Bbd75956100347c8664285D1</t>
-  </si>
-  <si>
-    <t>asdwqa12</t>
-  </si>
-  <si>
-    <t>0xA533F7729940DD9402da699aa8a9bD3281181FfC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -262,18 +265,6 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -283,27 +274,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -312,15 +288,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -655,288 +625,296 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F34DBE1-EA72-4533-97B0-9D4EFF35C954}">
-  <dimension ref="A1:B35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21573F96-787D-43CE-A4C4-3589456289B8}">
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B29" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B35" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="90.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="105.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9824A7-8A35-47C7-8872-1C8CFB59A5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7D15F6-F658-42A6-8A3D-E643231748AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>ManhACE</t>
   </si>
@@ -128,12 +128,6 @@
     <t>0xA533F7729940DD9402da699aa8a9bD3281181FfC</t>
   </si>
   <si>
-    <t>Number17</t>
-  </si>
-  <si>
-    <t>0xbD015CC6F657D0D2c54dE363A9117a7f2db147A1</t>
-  </si>
-  <si>
     <t>magisa</t>
   </si>
   <si>
@@ -218,9 +212,6 @@
     <t>0x479bF9bD2dEe2CFD235049F4718E5d9d31D5dB74</t>
   </si>
   <si>
-    <t>LuckyFox66</t>
-  </si>
-  <si>
     <t>ningyiyi</t>
   </si>
   <si>
@@ -243,6 +234,27 @@
   </si>
   <si>
     <t>0x88355C236580e126Bbd75956100347c8664285D1</t>
+  </si>
+  <si>
+    <t>iClow</t>
+  </si>
+  <si>
+    <t>0x08FA4F4B6a851635fAbC8186eDFA740649d9f266</t>
+  </si>
+  <si>
+    <t>FurryRemeo</t>
+  </si>
+  <si>
+    <t>0xdDB799B03FcA0F108Fe986308C8704A98f0f6B0f</t>
+  </si>
+  <si>
+    <t>TheLasT</t>
+  </si>
+  <si>
+    <t>0xD3609eE3fBCF7923b3B101E8AfB7b215459d7eF8</t>
+  </si>
+  <si>
+    <t>godiceyyds</t>
   </si>
 </sst>
 </file>
@@ -626,15 +638,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21573F96-787D-43CE-A4C4-3589456289B8}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -663,138 +675,138 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -823,42 +835,42 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -866,59 +878,68 @@
         <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7D15F6-F658-42A6-8A3D-E643231748AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14A08FC-D3AB-4828-840F-A9BBC23BB9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
   <si>
     <t>ManhACE</t>
   </si>
@@ -77,12 +77,6 @@
     <t>0x0a1364c754dfBcC04dfDCd84C4c771cA697FeD76</t>
   </si>
   <si>
-    <t>kenyek</t>
-  </si>
-  <si>
-    <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
-  </si>
-  <si>
     <t>Polestarr</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>0xdf01a3312df58fA7B689Ce3fa1eFd9c0422171Bf</t>
   </si>
   <si>
-    <t>chan9q</t>
-  </si>
-  <si>
     <t>Findlay</t>
   </si>
   <si>
@@ -188,73 +179,40 @@
     <t>0x824EDB61C934E23b3fe03865eD72fa35BFAe7693</t>
   </si>
   <si>
-    <t>OkamiPulsard</t>
-  </si>
-  <si>
-    <t>0x036f36547917798d440BB50232839EbC2b36A054</t>
-  </si>
-  <si>
-    <t>EVMs</t>
-  </si>
-  <si>
-    <t>0x4F64F34b61bf78b8aEDd31026B974BCB2bf73A35</t>
-  </si>
-  <si>
-    <t>Sazabi</t>
-  </si>
-  <si>
-    <t>0x04B0fc4784577C117CF1b4A18Bb7316072Aff59C</t>
-  </si>
-  <si>
-    <t>Plume</t>
-  </si>
-  <si>
-    <t>0x479bF9bD2dEe2CFD235049F4718E5d9d31D5dB74</t>
-  </si>
-  <si>
-    <t>ningyiyi</t>
-  </si>
-  <si>
-    <t>0x10AEF2E22EbCbCBA5f4C00122F14aEEE3E0452a7</t>
-  </si>
-  <si>
-    <t>Sumire</t>
-  </si>
-  <si>
-    <t>0x7f982521Aa5e3e0f16d6FF882623f98a316d0E70</t>
-  </si>
-  <si>
-    <t>iiTzWasabi</t>
-  </si>
-  <si>
-    <t>0xf33fc5245372149f26159C28cA674FE0169A1018</t>
-  </si>
-  <si>
-    <t>EliteArrow</t>
-  </si>
-  <si>
-    <t>0x88355C236580e126Bbd75956100347c8664285D1</t>
-  </si>
-  <si>
-    <t>iClow</t>
-  </si>
-  <si>
-    <t>0x08FA4F4B6a851635fAbC8186eDFA740649d9f266</t>
-  </si>
-  <si>
-    <t>FurryRemeo</t>
-  </si>
-  <si>
-    <t>0xdDB799B03FcA0F108Fe986308C8704A98f0f6B0f</t>
-  </si>
-  <si>
-    <t>TheLasT</t>
-  </si>
-  <si>
-    <t>0xD3609eE3fBCF7923b3B101E8AfB7b215459d7eF8</t>
-  </si>
-  <si>
-    <t>godiceyyds</t>
+    <t>Mitsuya</t>
+  </si>
+  <si>
+    <t>0xA5a0FeABD47B1865ba0a402abcfC810a7A560d06</t>
+  </si>
+  <si>
+    <t>JustADragon</t>
+  </si>
+  <si>
+    <t>0xAD418D90747Ba45CFdfE45547c5027D2c0945ECc</t>
+  </si>
+  <si>
+    <t>KitaKitsune</t>
+  </si>
+  <si>
+    <t>0x1a83fF0698FaaCef459BfB6945b7D23a0B0919Cd</t>
+  </si>
+  <si>
+    <t>Seriae</t>
+  </si>
+  <si>
+    <t>0x6c8Ed2278Ca4a14E992918248Dbd266BDECE5FD0</t>
+  </si>
+  <si>
+    <t>FirstLove</t>
+  </si>
+  <si>
+    <t>0x6c31Ba8f2d40C18FBF5d8CD4A94AD40c43B08eEf</t>
+  </si>
+  <si>
+    <t>mangudai</t>
+  </si>
+  <si>
+    <t>0x8583e7b7eB1aECe066bcF275aa5233a57e42206E</t>
   </si>
 </sst>
 </file>
@@ -643,26 +601,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -691,10 +649,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -707,10 +665,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -723,58 +681,58 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -787,114 +745,114 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -907,34 +865,34 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14A08FC-D3AB-4828-840F-A9BBC23BB9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E98385E-E194-4C01-AD4D-CEDA681B2812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
   <si>
     <t>ManhACE</t>
   </si>
@@ -213,6 +213,45 @@
   </si>
   <si>
     <t>0x8583e7b7eB1aECe066bcF275aa5233a57e42206E</t>
+  </si>
+  <si>
+    <t>kenyek</t>
+  </si>
+  <si>
+    <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
+  </si>
+  <si>
+    <t>MrChah</t>
+  </si>
+  <si>
+    <t>0x76aF3310cc411EcBB3f3E330bf8A612654daEdb5</t>
+  </si>
+  <si>
+    <t>HEROHERO</t>
+  </si>
+  <si>
+    <t>0xff6d12Ac34b8b5F9799b7f01cf24Bb26C172c5C1</t>
+  </si>
+  <si>
+    <t>SingJumpRap</t>
+  </si>
+  <si>
+    <t>0xe75cC9Be77419a05c0e2ADB5730CB9f7136B3221</t>
+  </si>
+  <si>
+    <t>OwOa</t>
+  </si>
+  <si>
+    <t>0xf28dc3c0e97943053433ffB71C394093AcB6e8d0</t>
+  </si>
+  <si>
+    <t>iMDB</t>
+  </si>
+  <si>
+    <t>0xf12cD0A73362B1610d8942d53d815B3Ec4a89476</t>
+  </si>
+  <si>
+    <t>lNursel</t>
   </si>
 </sst>
 </file>
@@ -596,8 +635,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21573F96-787D-43CE-A4C4-3589456289B8}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -892,6 +934,230 @@
         <v>56</v>
       </c>
       <c r="B37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>54</v>
+      </c>
+      <c r="B64" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" t="s">
         <v>57</v>
       </c>
     </row>

--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E98385E-E194-4C01-AD4D-CEDA681B2812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4DC2A5-BB83-47F7-AEEE-538C56FD4BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
   <si>
     <t>ManhACE</t>
   </si>
@@ -47,12 +47,6 @@
     <t>0x0d07c525829614509506c843813225342FE9023e</t>
   </si>
   <si>
-    <t>BIG1996</t>
-  </si>
-  <si>
-    <t>0x2722f1d45e7337bA945dfF885623eFf744fdE805</t>
-  </si>
-  <si>
     <t>LunLunSaint</t>
   </si>
   <si>
@@ -65,18 +59,6 @@
     <t>0x7292FC4dCeA35666d638A23F519406A5E634Fd05</t>
   </si>
   <si>
-    <t>MeiFu</t>
-  </si>
-  <si>
-    <t>0x93DcB573b9578D531B31cA1d6E33c935bA668423</t>
-  </si>
-  <si>
-    <t>LiuDeHua</t>
-  </si>
-  <si>
-    <t>0x0a1364c754dfBcC04dfDCd84C4c771cA697FeD76</t>
-  </si>
-  <si>
     <t>Polestarr</t>
   </si>
   <si>
@@ -110,12 +92,6 @@
     <t>0x99561e3080385C907c4A9B4bbB944508E8d1D15e</t>
   </si>
   <si>
-    <t>Osora</t>
-  </si>
-  <si>
-    <t>0x01e11d2925519f6C84EA49B6809f3D34b87a43Df</t>
-  </si>
-  <si>
     <t>asdwqa12</t>
   </si>
   <si>
@@ -128,49 +104,22 @@
     <t>0x6f6E91a883A9Ec32068302a4051B27C57E376A48</t>
   </si>
   <si>
-    <t>MrKun</t>
-  </si>
-  <si>
-    <t>0xcb5C82d2fd95C35d4CAe44a2a5CD44C9b1201A87</t>
-  </si>
-  <si>
     <t>INurseI</t>
   </si>
   <si>
     <t>0xbF543fB6fe42f1c54A01385298c29D3Fba735951</t>
   </si>
   <si>
-    <t>ShadowSAMA</t>
-  </si>
-  <si>
-    <t>0x1db18A653bd7C6C2dc899933340B7a960b451399</t>
-  </si>
-  <si>
     <t>NFT188</t>
   </si>
   <si>
     <t>0x34219BDBfDcB233FCe08185724435fDd40E89929</t>
   </si>
   <si>
-    <t>SoLUK</t>
-  </si>
-  <si>
-    <t>0x9bCeE51c0AEd896CAAb5fb6B7FB6630D1101Edd8</t>
-  </si>
-  <si>
-    <t>xQvQx</t>
-  </si>
-  <si>
-    <t>0xdf01a3312df58fA7B689Ce3fa1eFd9c0422171Bf</t>
-  </si>
-  <si>
     <t>Findlay</t>
   </si>
   <si>
     <t>0x0067365bDaA8DBFaa683C385623896fe5C5E83f3</t>
-  </si>
-  <si>
-    <t>0x76807A4d1b91eC1bF43B58d0776Bd8A1693b662c</t>
   </si>
   <si>
     <t>ptzO3O7</t>
@@ -635,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21573F96-787D-43CE-A4C4-3589456289B8}">
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
@@ -643,522 +592,226 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>68</v>
-      </c>
-      <c r="B59" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>21</v>
-      </c>
-      <c r="B62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>25</v>
-      </c>
-      <c r="B63" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/address-book.xlsx
+++ b/data/address-book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4DC2A5-BB83-47F7-AEEE-538C56FD4BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861D6B0F-07B4-4A53-A6AC-E8B853B5CC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{719AF457-8665-40AE-9ECA-E2C783C5C2E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>ManhACE</t>
   </si>
@@ -47,12 +47,6 @@
     <t>0x0d07c525829614509506c843813225342FE9023e</t>
   </si>
   <si>
-    <t>LunLunSaint</t>
-  </si>
-  <si>
-    <t>0x61b72F9dC73CaAD654fF9F24d9eEB11A2b730f45</t>
-  </si>
-  <si>
     <t>Powder</t>
   </si>
   <si>
@@ -86,12 +80,6 @@
     <t>0x940Fbb99e06A4eDBd403ec2BdaC652F6e5eadda3</t>
   </si>
   <si>
-    <t>Lightbringer</t>
-  </si>
-  <si>
-    <t>0x99561e3080385C907c4A9B4bbB944508E8d1D15e</t>
-  </si>
-  <si>
     <t>asdwqa12</t>
   </si>
   <si>
@@ -170,12 +158,6 @@
     <t>0x867d32Dc890B7C926c91A07c48E64610a940DD81</t>
   </si>
   <si>
-    <t>MrChah</t>
-  </si>
-  <si>
-    <t>0x76aF3310cc411EcBB3f3E330bf8A612654daEdb5</t>
-  </si>
-  <si>
     <t>HEROHERO</t>
   </si>
   <si>
@@ -201,6 +183,72 @@
   </si>
   <si>
     <t>lNursel</t>
+  </si>
+  <si>
+    <t>JJSPKK</t>
+  </si>
+  <si>
+    <t>0x4f1803C7836cd270F258b4Ac800819062138a64a</t>
+  </si>
+  <si>
+    <t>CYuXuan</t>
+  </si>
+  <si>
+    <t>0x1f2dC637f55909B3850F780F636Db941ee980fe2</t>
+  </si>
+  <si>
+    <t>LockU</t>
+  </si>
+  <si>
+    <t>0x258B3C01e607448AaA60D89EBF3E665FB703b958</t>
+  </si>
+  <si>
+    <t>Lynene</t>
+  </si>
+  <si>
+    <t>0xFd113460637b319332b1E948cd40E89FEE382260</t>
+  </si>
+  <si>
+    <t>ShadowSAMA</t>
+  </si>
+  <si>
+    <t>0x1db18A653bd7C6C2dc899933340B7a960b451399</t>
+  </si>
+  <si>
+    <t>godiceyyds</t>
+  </si>
+  <si>
+    <t>0xdDB799B03FcA0F108Fe986308C8704A98f0f6B0f</t>
+  </si>
+  <si>
+    <t>LiuDeHua</t>
+  </si>
+  <si>
+    <t>0x0a1364c754dfBcC04dfDCd84C4c771cA697FeD76</t>
+  </si>
+  <si>
+    <t>TheLasT</t>
+  </si>
+  <si>
+    <t>0xD3609eE3fBCF7923b3B101E8AfB7b215459d7eF8</t>
+  </si>
+  <si>
+    <t>arknights</t>
+  </si>
+  <si>
+    <t>0x0A28aEC269C17C5bAc15593961C46107e6aBAb29</t>
+  </si>
+  <si>
+    <t>Thunnini</t>
+  </si>
+  <si>
+    <t>0x79Ece4Ab4451fd55189bE43016c3d630a9DDb106</t>
+  </si>
+  <si>
+    <t>RichardV2</t>
+  </si>
+  <si>
+    <t>0xdef398F75F6FAB257E7027c2beAE62901DDFEA27</t>
   </si>
 </sst>
 </file>
@@ -584,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21573F96-787D-43CE-A4C4-3589456289B8}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
@@ -592,82 +640,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -680,119 +728,119 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>18</v>
@@ -800,18 +848,82 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B33" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
